--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486932_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486932_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. MUKENDI MUKENDI</t>
+          <t>A. LÓPEZ MARTINEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.0326</v>
+        <v>0.8141</v>
       </c>
       <c r="E2" t="n">
-        <v>1.8756</v>
+        <v>0.2401</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.843</v>
+        <v>0.574</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.6511</v>
+        <v>0.667</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.3461</v>
+        <v>-0.2013</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.305</v>
+        <v>0.8682</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.3575</v>
+        <v>0.585</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.5153</v>
+        <v>0.0195</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1579</v>
+        <v>0.5656</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.2937</v>
+        <v>0.0819</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.8308</v>
+        <v>-0.2208</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.4629</v>
+        <v>0.3027</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.616</v>
+        <v>0.8214</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.0534</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.4374</v>
+        <v>0.8214</v>
       </c>
       <c r="S2" t="n">
-        <v>1.6407</v>
+        <v>-0.434</v>
       </c>
       <c r="T2" t="n">
-        <v>1.4488</v>
+        <v>-0.3449</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1919</v>
+        <v>-0.0891</v>
       </c>
       <c r="V2" t="n">
-        <v>1.6591</v>
+        <v>-0.2402</v>
       </c>
       <c r="W2" t="n">
-        <v>2.8377</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.1786</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. LÓPEZ MARTINEZ</t>
+          <t>M. MUKENDI MUKENDI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5003</v>
+        <v>0.0089</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0737</v>
+        <v>1.0001</v>
       </c>
       <c r="F3" t="n">
-        <v>0.574</v>
+        <v>-0.9912</v>
       </c>
       <c r="G3" t="n">
-        <v>0.667</v>
+        <v>-1.6511</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.2013</v>
+        <v>-1.3461</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8682</v>
+        <v>-0.305</v>
       </c>
       <c r="J3" t="n">
-        <v>0.585</v>
+        <v>-0.3575</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0195</v>
+        <v>-0.5153</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5656</v>
+        <v>0.1579</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0819</v>
+        <v>-1.2937</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2208</v>
+        <v>-0.8308</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3027</v>
+        <v>-0.4629</v>
       </c>
       <c r="P3" t="n">
-        <v>0.8214</v>
+        <v>-0.616</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-2.0534</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8214</v>
+        <v>1.4374</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7478</v>
+        <v>0.6169</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6587</v>
+        <v>0.5732</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0891</v>
+        <v>0.0437</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.2402</v>
+        <v>1.6591</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.8377</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2402</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.3387</v>
+        <v>-1.3684</v>
       </c>
       <c r="E4" t="n">
         <v>-1.8169</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4782</v>
+        <v>0.4485</v>
       </c>
       <c r="G4" t="n">
         <v>-0.4899</v>
@@ -766,13 +766,13 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1779</v>
+        <v>0.1482</v>
       </c>
       <c r="T4" t="n">
         <v>-0.1317</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3096</v>
+        <v>0.28</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. HERNANDEZ MARTINEZ</t>
+          <t>P. CAMPENY LLOVERAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.8523</v>
+        <v>-1.4882</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9764</v>
+        <v>1.1481</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.8287</v>
+        <v>-2.6364</v>
       </c>
       <c r="G5" t="n">
-        <v>3.088</v>
+        <v>-3.1922</v>
       </c>
       <c r="H5" t="n">
-        <v>1.6251</v>
+        <v>-0.0323</v>
       </c>
       <c r="I5" t="n">
-        <v>1.4629</v>
+        <v>-3.1599</v>
       </c>
       <c r="J5" t="n">
-        <v>4.971</v>
+        <v>0.3537</v>
       </c>
       <c r="K5" t="n">
-        <v>2.5111</v>
+        <v>1.0775</v>
       </c>
       <c r="L5" t="n">
-        <v>2.4599</v>
+        <v>-0.7238</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.883</v>
+        <v>-3.5459</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.886</v>
+        <v>-1.1098</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.997</v>
+        <v>-2.4362</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.6694</v>
+        <v>1.2321</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.0801</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4107</v>
+        <v>1.2321</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5029</v>
+        <v>0.3631</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9145</v>
+        <v>0.2051</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4116</v>
+        <v>0.158</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.7679</v>
+        <v>0.1088</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.5893</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.7679</v>
+        <v>-0.4805</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. CAMPENY LLOVERAS</t>
+          <t>F. HERNANDEZ MARTINEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.9115</v>
+        <v>-1.5838</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8731</v>
+        <v>1.1856</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.7846</v>
+        <v>-2.7694</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.1922</v>
+        <v>3.088</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0323</v>
+        <v>1.6251</v>
       </c>
       <c r="I6" t="n">
-        <v>-3.1599</v>
+        <v>1.4629</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3537</v>
+        <v>4.971</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0775</v>
+        <v>2.5111</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.7238</v>
+        <v>2.4599</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.5459</v>
+        <v>-1.883</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.1098</v>
+        <v>-0.886</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.4362</v>
+        <v>-0.997</v>
       </c>
       <c r="P6" t="n">
-        <v>1.2321</v>
+        <v>-2.6694</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-3.0801</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2321</v>
+        <v>0.4107</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0602</v>
+        <v>-0.2344</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0699</v>
+        <v>-0.7053</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0098</v>
+        <v>0.4709</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1088</v>
+        <v>-1.7679</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5893</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.4805</v>
+        <v>-1.7679</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.9151</v>
+        <v>-1.6466</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.182</v>
+        <v>0.0272</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.7331</v>
+        <v>-1.6739</v>
       </c>
       <c r="G7" t="n">
         <v>-1.6869</v>
@@ -1000,13 +1000,13 @@
         <v>0.616</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4952</v>
+        <v>-0.2267</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3952</v>
+        <v>-0.186</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0999</v>
+        <v>-0.0407</v>
       </c>
       <c r="V7" t="n">
         <v>-0.3491</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.9966</v>
+        <v>-3.4143</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6671</v>
+        <v>-0.1441</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.3295</v>
+        <v>-3.2702</v>
       </c>
       <c r="G8" t="n">
         <v>-1.5056</v>
@@ -1078,13 +1078,13 @@
         <v>1.4374</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0453</v>
+        <v>-0.463</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7091</v>
+        <v>-0.1861</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3362</v>
+        <v>-0.2769</v>
       </c>
       <c r="V8" t="n">
         <v>-0.8295</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. TIMONER GIMENEZ</t>
+          <t>R. MARTÍNEZ-QUINTANILLA JIMÉNEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.2015</v>
+        <v>-3.9471</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.808</v>
+        <v>-1.9521</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.3936</v>
+        <v>-1.995</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.6288</v>
+        <v>-3.0512</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.0525</v>
+        <v>-0.7461</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5763</v>
+        <v>-2.3051</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.8431</v>
+        <v>-2.3201</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.0531</v>
+        <v>-0.3859</v>
       </c>
       <c r="L9" t="n">
-        <v>1.21</v>
+        <v>-1.9342</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.7857</v>
+        <v>-0.7311</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9994</v>
+        <v>-0.3602</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.7863</v>
+        <v>-0.3709</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.616</v>
+        <v>0.616</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4107</v>
+        <v>0.616</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2835</v>
+        <v>0.1472</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0618</v>
+        <v>0.368</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2217</v>
+        <v>-0.2208</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2402</v>
+        <v>-1.6591</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2402</v>
+        <v>-1.6591</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. MARTÍNEZ-QUINTANILLA JIMÉNEZ</t>
+          <t>R. TIMONER GIMENEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.5499</v>
+        <v>-4.3902</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.4364</v>
+        <v>-2.0559</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.1136</v>
+        <v>-2.3343</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.0512</v>
+        <v>-3.6288</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.7461</v>
+        <v>-3.0525</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.3051</v>
+        <v>-0.5763</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.3201</v>
+        <v>-0.8431</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.3859</v>
+        <v>-2.0531</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.9342</v>
+        <v>1.21</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.7311</v>
+        <v>-2.7857</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3602</v>
+        <v>-0.9994</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3709</v>
+        <v>-1.7863</v>
       </c>
       <c r="P10" t="n">
-        <v>0.616</v>
+        <v>-0.616</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R10" t="n">
-        <v>0.616</v>
+        <v>0.4107</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4557</v>
+        <v>0.0948</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1163</v>
+        <v>-0.1861</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3394</v>
+        <v>0.281</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.6591</v>
+        <v>-0.2402</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.6591</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C. TOLEDO ZAMORA</t>
+          <t>J. TAVELLI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.673</v>
+        <v>-4.4634</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.2986</v>
+        <v>-1.401</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.3745</v>
+        <v>-3.0624</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.3052</v>
+        <v>-1.5651</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.832</v>
+        <v>-0.0259</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.4733</v>
+        <v>-1.5392</v>
       </c>
       <c r="J11" t="n">
-        <v>0.535</v>
+        <v>-0.4369</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.3329</v>
+        <v>0.221</v>
       </c>
       <c r="L11" t="n">
-        <v>1.8679</v>
+        <v>-0.6579</v>
       </c>
       <c r="M11" t="n">
-        <v>-4.8403</v>
+        <v>-1.1281</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.4991</v>
+        <v>-0.2468</v>
       </c>
       <c r="O11" t="n">
-        <v>-3.3412</v>
+        <v>-0.8813</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.4107</v>
+        <v>-0.8214</v>
       </c>
       <c r="Q11" t="n">
         <v>-2.0534</v>
       </c>
       <c r="R11" t="n">
-        <v>1.6427</v>
+        <v>1.2321</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2606</v>
+        <v>-0.309</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4375</v>
+        <v>-0.0892</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.177</v>
+        <v>-0.2198</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.2177</v>
+        <v>-1.7679</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.2177</v>
+        <v>1.1786</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-2.9466</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. TAVELLI</t>
+          <t>C. TOLEDO ZAMORA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.1799</v>
+        <v>-4.832</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.0286</v>
+        <v>-1.5465</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.1514</v>
+        <v>-3.2856</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.5651</v>
+        <v>-4.3052</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.0259</v>
+        <v>-2.832</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.5392</v>
+        <v>-1.4733</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.4369</v>
+        <v>0.535</v>
       </c>
       <c r="K12" t="n">
-        <v>0.221</v>
+        <v>-1.3329</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6579</v>
+        <v>1.8679</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.1281</v>
+        <v>-4.8403</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.2468</v>
+        <v>-1.4991</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.8813</v>
+        <v>-3.3412</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.8214</v>
+        <v>-0.4107</v>
       </c>
       <c r="Q12" t="n">
         <v>-2.0534</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2321</v>
+        <v>1.6427</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0256</v>
+        <v>0.1016</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7169</v>
+        <v>0.1896</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3087</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.7679</v>
+        <v>-0.2177</v>
       </c>
       <c r="W12" t="n">
-        <v>1.1786</v>
+        <v>-0.2177</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.9466</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.1274</v>
+        <v>-8.572800000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.6645</v>
+        <v>-5.6059</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.463</v>
+        <v>-2.9669</v>
       </c>
       <c r="G13" t="n">
         <v>-10.2401</v>
@@ -1468,13 +1468,13 @@
         <v>1.4374</v>
       </c>
       <c r="S13" t="n">
-        <v>1.8724</v>
+        <v>0.4271</v>
       </c>
       <c r="T13" t="n">
-        <v>0.9877</v>
+        <v>0.0463</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8847</v>
+        <v>0.3808</v>
       </c>
       <c r="V13" t="n">
         <v>0.8295</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-35.21299999999999</v>
+        <v>-34.8838</v>
       </c>
       <c r="E14" t="n">
-        <v>-11.2507</v>
+        <v>-10.9213</v>
       </c>
       <c r="F14" t="n">
         <v>-23.9628</v>
@@ -1525,13 +1525,13 @@
         <v>-7.1489</v>
       </c>
       <c r="L14" t="n">
-        <v>3.234000000000001</v>
+        <v>3.234</v>
       </c>
       <c r="M14" t="n">
         <v>-23.6461</v>
       </c>
       <c r="N14" t="n">
-        <v>-8.453700000000001</v>
+        <v>-8.4537</v>
       </c>
       <c r="O14" t="n">
         <v>-15.1925</v>
@@ -1546,13 +1546,13 @@
         <v>11.2939</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.09759999999999991</v>
+        <v>0.2317999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7765000000000002</v>
+        <v>-0.4470999999999998</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6790000000000002</v>
+        <v>0.6791000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>-4.4742</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. MONTILLA DIAZ</t>
+          <t>G. PEREZ RAMIREZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.7431</v>
+        <v>7.8735</v>
       </c>
       <c r="E15" t="n">
-        <v>5.1994</v>
+        <v>5.9489</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5437</v>
+        <v>1.9245</v>
       </c>
       <c r="G15" t="n">
-        <v>4.291</v>
+        <v>6.0554</v>
       </c>
       <c r="H15" t="n">
-        <v>2.9492</v>
+        <v>1.2907</v>
       </c>
       <c r="I15" t="n">
-        <v>1.3418</v>
+        <v>4.7646</v>
       </c>
       <c r="J15" t="n">
-        <v>3.7853</v>
+        <v>6.3597</v>
       </c>
       <c r="K15" t="n">
-        <v>3.1408</v>
+        <v>0.5061</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6445</v>
+        <v>5.8536</v>
       </c>
       <c r="M15" t="n">
-        <v>0.5057</v>
+        <v>-0.3043</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1917</v>
+        <v>0.7846</v>
       </c>
       <c r="O15" t="n">
-        <v>0.6974</v>
+        <v>-1.089</v>
       </c>
       <c r="P15" t="n">
-        <v>1.4374</v>
+        <v>1.6427</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4374</v>
+        <v>1.6427</v>
       </c>
       <c r="S15" t="n">
-        <v>1.0147</v>
+        <v>0.1754</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9336</v>
+        <v>-0.4108</v>
       </c>
       <c r="U15" t="n">
-        <v>0.08110000000000001</v>
+        <v>0.5861</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.4805</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.4805</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. PEREZ RAMIREZ</t>
+          <t>M. MONTILLA DIAZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.5781</v>
+        <v>6.1207</v>
       </c>
       <c r="E16" t="n">
-        <v>5.6351</v>
+        <v>4.4672</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9429</v>
+        <v>1.6535</v>
       </c>
       <c r="G16" t="n">
-        <v>6.0554</v>
+        <v>4.291</v>
       </c>
       <c r="H16" t="n">
-        <v>1.2907</v>
+        <v>2.9492</v>
       </c>
       <c r="I16" t="n">
-        <v>4.7646</v>
+        <v>1.3418</v>
       </c>
       <c r="J16" t="n">
-        <v>6.3597</v>
+        <v>3.7853</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5061</v>
+        <v>3.1408</v>
       </c>
       <c r="L16" t="n">
-        <v>5.8536</v>
+        <v>0.6445</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.3043</v>
+        <v>0.5057</v>
       </c>
       <c r="N16" t="n">
-        <v>0.7846</v>
+        <v>-0.1917</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.089</v>
+        <v>0.6974</v>
       </c>
       <c r="P16" t="n">
-        <v>1.6427</v>
+        <v>1.4374</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.6427</v>
+        <v>1.4374</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.1201</v>
+        <v>0.3923</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7246</v>
+        <v>0.2014</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3955</v>
+        <v>0.1909</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.4805</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.4805</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. BITJAA KODY</t>
+          <t>K. GREELEY</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.633</v>
+        <v>5.5543</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2106</v>
+        <v>4.1097</v>
       </c>
       <c r="F17" t="n">
-        <v>4.4224</v>
+        <v>1.4445</v>
       </c>
       <c r="G17" t="n">
-        <v>3.8896</v>
+        <v>3.4225</v>
       </c>
       <c r="H17" t="n">
-        <v>3.6134</v>
+        <v>1.6255</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2763</v>
+        <v>1.797</v>
       </c>
       <c r="J17" t="n">
-        <v>3.1518</v>
+        <v>3.8533</v>
       </c>
       <c r="K17" t="n">
-        <v>2.297</v>
+        <v>1.3145</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8548</v>
+        <v>2.5388</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7378</v>
+        <v>-0.4308</v>
       </c>
       <c r="N17" t="n">
-        <v>1.3164</v>
+        <v>0.311</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5786</v>
+        <v>-0.7418</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.2053</v>
+        <v>0.2053</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.0534</v>
+        <v>-1.0267</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8481</v>
+        <v>1.2321</v>
       </c>
       <c r="S17" t="n">
-        <v>2.189</v>
+        <v>0.5076000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1122</v>
+        <v>-0.1357</v>
       </c>
       <c r="U17" t="n">
-        <v>2.0767</v>
+        <v>0.6433</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.2402</v>
+        <v>1.4189</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.4189</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2402</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>K. GREELEY</t>
+          <t>J. BITJAA KODY</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>5.3729</v>
+        <v>4.6967</v>
       </c>
       <c r="E18" t="n">
-        <v>4.4236</v>
+        <v>1.2106</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9494</v>
+        <v>3.486</v>
       </c>
       <c r="G18" t="n">
-        <v>3.4225</v>
+        <v>3.8896</v>
       </c>
       <c r="H18" t="n">
-        <v>1.6255</v>
+        <v>3.6134</v>
       </c>
       <c r="I18" t="n">
-        <v>1.797</v>
+        <v>0.2763</v>
       </c>
       <c r="J18" t="n">
-        <v>3.8533</v>
+        <v>3.1518</v>
       </c>
       <c r="K18" t="n">
-        <v>1.3145</v>
+        <v>2.297</v>
       </c>
       <c r="L18" t="n">
-        <v>2.5388</v>
+        <v>0.8548</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4308</v>
+        <v>0.7378</v>
       </c>
       <c r="N18" t="n">
-        <v>0.311</v>
+        <v>1.3164</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.7418</v>
+        <v>-0.5786</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2053</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0267</v>
+        <v>-2.0534</v>
       </c>
       <c r="R18" t="n">
-        <v>1.2321</v>
+        <v>1.8481</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3262</v>
+        <v>1.2526</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1781</v>
+        <v>0.1122</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1481</v>
+        <v>1.1404</v>
       </c>
       <c r="V18" t="n">
-        <v>1.4189</v>
+        <v>-0.2402</v>
       </c>
       <c r="W18" t="n">
-        <v>1.4189</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. ILINCIC</t>
+          <t>C. HURTADO CERVANTES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.9931</v>
+        <v>4.164</v>
       </c>
       <c r="E19" t="n">
-        <v>2.5832</v>
+        <v>2.9253</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4099</v>
+        <v>1.2388</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.3181</v>
+        <v>-1.4717</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.4866</v>
+        <v>0.1361</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8315</v>
+        <v>-1.6077</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.3633</v>
+        <v>-2.2777</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6</v>
+        <v>-0.3436</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.7633</v>
+        <v>-1.9342</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0452</v>
+        <v>0.8061</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1134</v>
+        <v>0.4796</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0682</v>
+        <v>0.3264</v>
       </c>
       <c r="P19" t="n">
-        <v>1.0267</v>
+        <v>1.2321</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.0267</v>
+        <v>1.2321</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5084</v>
+        <v>-0.3109</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1704</v>
+        <v>-0.1008</v>
       </c>
       <c r="U19" t="n">
-        <v>0.338</v>
+        <v>-0.21</v>
       </c>
       <c r="V19" t="n">
-        <v>3.7761</v>
+        <v>4.7145</v>
       </c>
       <c r="W19" t="n">
-        <v>3.7761</v>
+        <v>5.3038</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.5893</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C. HURTADO CERVANTES</t>
+          <t>D. ILINCIC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>3.4579</v>
+        <v>3.7211</v>
       </c>
       <c r="E20" t="n">
-        <v>2.5069</v>
+        <v>2.2694</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9510999999999999</v>
+        <v>1.4517</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.4717</v>
+        <v>-1.3181</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1361</v>
+        <v>-0.4866</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.6077</v>
+        <v>-0.8315</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.2777</v>
+        <v>-1.3633</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.3436</v>
+        <v>-0.6</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.9342</v>
+        <v>-0.7633</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8061</v>
+        <v>0.0452</v>
       </c>
       <c r="N20" t="n">
-        <v>0.4796</v>
+        <v>0.1134</v>
       </c>
       <c r="O20" t="n">
-        <v>0.3264</v>
+        <v>-0.0682</v>
       </c>
       <c r="P20" t="n">
-        <v>1.2321</v>
+        <v>1.0267</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2321</v>
+        <v>1.0267</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.017</v>
+        <v>0.2363</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5192</v>
+        <v>-0.1434</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4977</v>
+        <v>0.3798</v>
       </c>
       <c r="V20" t="n">
-        <v>4.7145</v>
+        <v>3.7761</v>
       </c>
       <c r="W20" t="n">
-        <v>5.3038</v>
+        <v>3.7761</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5893</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2.5365</v>
+        <v>2.8731</v>
       </c>
       <c r="E21" t="n">
-        <v>4.0208</v>
+        <v>3.8116</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.4843</v>
+        <v>-0.9386</v>
       </c>
       <c r="G21" t="n">
         <v>2.5223</v>
@@ -2092,13 +2092,13 @@
         <v>1.4374</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0043</v>
+        <v>0.3322</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1704</v>
+        <v>-0.0388</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1747</v>
+        <v>0.371</v>
       </c>
       <c r="V21" t="n">
         <v>-1.4189</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. MOLINA MARTINEZ</t>
+          <t>A. BELLVER VALIENTE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.6838</v>
+        <v>1.9865</v>
       </c>
       <c r="E22" t="n">
-        <v>1.3038</v>
+        <v>0.2898</v>
       </c>
       <c r="F22" t="n">
-        <v>0.38</v>
+        <v>1.6968</v>
       </c>
       <c r="G22" t="n">
-        <v>1.8504</v>
+        <v>6.5126</v>
       </c>
       <c r="H22" t="n">
-        <v>1.9688</v>
+        <v>1.1318</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1184</v>
+        <v>5.3807</v>
       </c>
       <c r="J22" t="n">
-        <v>2.0866</v>
+        <v>4.478</v>
       </c>
       <c r="K22" t="n">
-        <v>1.3237</v>
+        <v>0.0973</v>
       </c>
       <c r="L22" t="n">
-        <v>0.7629</v>
+        <v>4.3807</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.2361</v>
+        <v>2.0345</v>
       </c>
       <c r="N22" t="n">
-        <v>0.6452</v>
+        <v>1.0345</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.8813</v>
+        <v>1</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>-2.8748</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.0267</v>
+        <v>-4.1068</v>
       </c>
       <c r="R22" t="n">
-        <v>1.0267</v>
+        <v>1.2321</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0736</v>
+        <v>-0.4726</v>
       </c>
       <c r="T22" t="n">
-        <v>0.244</v>
+        <v>-0.0814</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1704</v>
+        <v>-0.3912</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.2402</v>
+        <v>-1.1786</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.2402</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. BELLVER VALIENTE</t>
+          <t>J. MOLINA MARTINEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>1.2543</v>
+        <v>1.6664</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.024</v>
+        <v>0.99</v>
       </c>
       <c r="F23" t="n">
-        <v>1.2784</v>
+        <v>0.6764</v>
       </c>
       <c r="G23" t="n">
-        <v>6.5126</v>
+        <v>1.8504</v>
       </c>
       <c r="H23" t="n">
-        <v>1.1318</v>
+        <v>1.9688</v>
       </c>
       <c r="I23" t="n">
-        <v>5.3807</v>
+        <v>-0.1184</v>
       </c>
       <c r="J23" t="n">
-        <v>4.478</v>
+        <v>2.0866</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0973</v>
+        <v>1.3237</v>
       </c>
       <c r="L23" t="n">
-        <v>4.3807</v>
+        <v>0.7629</v>
       </c>
       <c r="M23" t="n">
-        <v>2.0345</v>
+        <v>-0.2361</v>
       </c>
       <c r="N23" t="n">
-        <v>1.0345</v>
+        <v>0.6452</v>
       </c>
       <c r="O23" t="n">
-        <v>1</v>
+        <v>-0.8813</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.8748</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>-4.1068</v>
+        <v>-1.0267</v>
       </c>
       <c r="R23" t="n">
-        <v>1.2321</v>
+        <v>1.0267</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2048</v>
+        <v>0.0562</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3952</v>
+        <v>-0.0698</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8096</v>
+        <v>0.126</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.1786</v>
+        <v>-0.2402</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.1786</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.6323</v>
+        <v>0.892</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4892</v>
+        <v>0.6984</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1431</v>
+        <v>0.1936</v>
       </c>
       <c r="G24" t="n">
         <v>-0.5173</v>
@@ -2326,13 +2326,13 @@
         <v>1.0267</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1229</v>
+        <v>0.3826</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.527</v>
+        <v>-0.3178</v>
       </c>
       <c r="U24" t="n">
-        <v>0.6499</v>
+        <v>0.7004</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2087</v>
+        <v>0.8129</v>
       </c>
       <c r="E25" t="n">
-        <v>0.06909999999999999</v>
+        <v>0.5921999999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.2778</v>
+        <v>0.2208</v>
       </c>
       <c r="G25" t="n">
         <v>2.6839</v>
@@ -2404,13 +2404,13 @@
         <v>1.0267</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.7755</v>
+        <v>0.2461</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2558</v>
+        <v>0.2673</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.5197000000000001</v>
+        <v>-0.0211</v>
       </c>
       <c r="V25" t="n">
         <v>-2.117</v>
@@ -2437,10 +2437,10 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.4632</v>
+        <v>-2.3586</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.4551</v>
+        <v>-3.3505</v>
       </c>
       <c r="F26" t="n">
         <v>0.9918</v>
@@ -2482,10 +2482,10 @@
         <v>0.2053</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.0155</v>
+        <v>0.0891</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.0659</v>
+        <v>0.0387</v>
       </c>
       <c r="U26" t="n">
         <v>0.0504</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>35.2131</v>
+        <v>38.0026</v>
       </c>
       <c r="E27" t="n">
         <v>23.96259999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>11.2506</v>
+        <v>14.0398</v>
       </c>
       <c r="G27" t="n">
         <v>27.5611</v>
@@ -2551,7 +2551,7 @@
         <v>-3.2341</v>
       </c>
       <c r="P27" t="n">
-        <v>3.0801</v>
+        <v>3.080099999999999</v>
       </c>
       <c r="Q27" t="n">
         <v>-11.2937</v>
@@ -2560,13 +2560,13 @@
         <v>14.374</v>
       </c>
       <c r="S27" t="n">
-        <v>0.09759999999999987</v>
+        <v>2.886900000000001</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.679</v>
+        <v>-0.6788999999999999</v>
       </c>
       <c r="U27" t="n">
-        <v>0.7766000000000002</v>
+        <v>3.566</v>
       </c>
       <c r="V27" t="n">
         <v>4.474400000000001</v>
